--- a/p_parameters/archive_parameters/codebooks/D3_incidence_con_caratterizzazione.xlsx
+++ b/p_parameters/archive_parameters/codebooks/D3_incidence_con_caratterizzazione.xlsx
@@ -20,135 +20,210 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
-  <si>
-    <t xml:space="preserve">varname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codelist</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
+  <si>
+    <t xml:space="preserve">parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
   </si>
   <si>
     <t xml:space="preserve">howmany</t>
   </si>
   <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component</t>
+  </si>
+  <si>
     <t xml:space="preserve">IHD</t>
   </si>
   <si>
+    <t xml:space="preserve">componente di CV: cardiopatia ischemica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componente di CV: infarto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bypass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componente di CV: bypass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">angioplastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componente di CV: angioplastica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STROKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componente di cerebro: pregresso ictus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componente di cerebro: TIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componente di cerebro: rivascolarizzazione carotidea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arteriopatia periferica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ateros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component of Cvrisk:  aterosclerosi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">organdamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component of Cvrisk: organ damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dyslipidemia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component of Cvriskfactors: dyslipidemia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obesity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component of Cvriskfactors: obesity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component of Cvriskfactors: hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component of Cvriskfactors: smoking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scompenso cardiaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENDIS_Alg1_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component of Cvrisk RENDIS_Alg1: first group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENDIS_Alg1_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component of Cvrisk RENDIS_Alg1: second group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENDIS_Alg1_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component of Cvrisk RENDIS_Alg1: third group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENDIS_Alg2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component to renal: algorithm 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">met</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso di metformina nei 2 anni precedenti la data indice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">antidiabother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso di altri antidiabetici nei 2 anni precedenti la data indice (esclusa metformina)</t>
+  </si>
+  <si>
     <t xml:space="preserve">med_IHD</t>
   </si>
   <si>
     <t xml:space="preserve">dia_IHD</t>
   </si>
   <si>
-    <t xml:space="preserve">AMI</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_AMI</t>
   </si>
   <si>
-    <t xml:space="preserve">bypass</t>
-  </si>
-  <si>
     <t xml:space="preserve">proc_bypass</t>
   </si>
   <si>
-    <t xml:space="preserve">angioplastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proc_angioplastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STROKE</t>
+    <t xml:space="preserve">proc_angioplasty</t>
   </si>
   <si>
     <t xml:space="preserve">dia_STROKE</t>
   </si>
   <si>
-    <t xml:space="preserve">TIA</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_TIA</t>
   </si>
   <si>
-    <t xml:space="preserve">carot</t>
-  </si>
-  <si>
     <t xml:space="preserve">proc_carot</t>
   </si>
   <si>
-    <t xml:space="preserve">aop</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_aop</t>
   </si>
   <si>
-    <t xml:space="preserve">ateros</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_ateros</t>
   </si>
   <si>
-    <t xml:space="preserve">organdamage</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_organdamage</t>
   </si>
   <si>
-    <t xml:space="preserve">dyslipidemia</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_dyslipidemia</t>
   </si>
   <si>
-    <t xml:space="preserve">med_dislypidemia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obesity</t>
+    <t xml:space="preserve">med_dyslipidemia</t>
   </si>
   <si>
     <t xml:space="preserve">dia_obesity</t>
   </si>
   <si>
-    <t xml:space="preserve">hypertension</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_hypertension</t>
   </si>
   <si>
     <t xml:space="preserve">med_hypertension</t>
   </si>
   <si>
-    <t xml:space="preserve">smoking</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_smoking</t>
   </si>
   <si>
-    <t xml:space="preserve">HF</t>
-  </si>
-  <si>
     <t xml:space="preserve">dia_HF</t>
   </si>
   <si>
-    <t xml:space="preserve">RENDIS_Alg1_1</t>
-  </si>
-  <si>
     <t xml:space="preserve">med_RENDIS_Alg1_1</t>
   </si>
   <si>
-    <t xml:space="preserve">RENDIS_Alg1_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">med_RENDIS_Alg1_2</t>
   </si>
   <si>
-    <t xml:space="preserve">RENDIS_Alg1_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">med_RENDIS_Alg1_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RENDIS_Alg2</t>
   </si>
   <si>
     <t xml:space="preserve">med_RENDIS_Alg2</t>
@@ -303,11 +378,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -392,7 +467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.09"/>
@@ -401,7 +476,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.91"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -411,264 +486,557 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="A2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="0"/>
+      <c r="D6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="0"/>
+      <c r="D8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="0"/>
+      <c r="D10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="0"/>
+      <c r="D11" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="0"/>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="0"/>
+      <c r="D13" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="0"/>
+      <c r="D14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="0"/>
+      <c r="D15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="0"/>
+      <c r="D17" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="0"/>
+      <c r="D18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="0"/>
+      <c r="D19" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="0"/>
+      <c r="D20" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="0"/>
+      <c r="D21" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="0"/>
+      <c r="D22" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="B34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="B36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="B37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B38" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="B39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="B41" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="7" t="s">
+      <c r="B44" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-    </row>
+      <c r="B46" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
